--- a/test_parts.xlsx
+++ b/test_parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\warehouse_mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A9991FD-143F-4C85-865F-0337AE90DD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791DB4A3-2915-40DA-AA91-78FD97206757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A48A8ABB-CF4D-4D2F-97BA-E472414F5723}"/>
   </bookViews>
@@ -37,11 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
-  <si>
-    <t>簽收人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
   <si>
     <t>品牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,79 +48,54 @@
   </si>
   <si>
     <t>1769-IQ32</t>
+  </si>
+  <si>
+    <t>1756-OF8</t>
+  </si>
+  <si>
+    <t>料件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>新增料件</t>
+    <t>數量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1756-EN2TR</t>
+  </si>
+  <si>
+    <t>1756-RM2</t>
+  </si>
+  <si>
     <t>1756-RMC1</t>
+  </si>
+  <si>
+    <t>1756-A17</t>
+  </si>
+  <si>
+    <t>1756-IB32</t>
+  </si>
+  <si>
+    <t>1756-OB32</t>
+  </si>
+  <si>
+    <t>1756-IF16</t>
+  </si>
+  <si>
+    <t>1756-TBCH</t>
+  </si>
+  <si>
+    <t>1756-N2</t>
+  </si>
+  <si>
+    <t>1756-PAR2</t>
+  </si>
+  <si>
+    <t>工號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RM MODULE FIBER CABLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-A17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>17 SLOP CONTRLLOGIX CHASSIS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-IB32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-31 VDC INPUT 32 PTS (36 PIN)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-OB32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-31 VDC OUTPUT 32 PTS (36 PIN)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-IF16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ANALOG INPUT-CURRENT/VOLTAGE 16 PTS (36 PIN)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-OF8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ANALOG OUTPUT-CURRENT/VOLTAGE 8 PTS (20 PIN)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-TBCH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>36 PIN SCREW CLAMP BLOCK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756-N2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EMPTY SLOT FILLER CARD (ONE FILLER PER PACKAGE)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompactLogix 32 Point Digital Input</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>J115-05-192</t>
   </si>
 </sst>
 </file>
@@ -507,137 +478,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DEB820-F7AC-4A8C-99B5-D02FB059DDD1}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="60.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4">
+        <v>40</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4">
+        <v>8</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C4" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C6" s="4">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C7" s="4">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C8" s="4">
+        <v>79</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="4">
+        <v>41</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="4">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="4">
+        <v>310</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4">
+        <v>129</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
